--- a/docs/registers/beatmind-registers.xlsx
+++ b/docs/registers/beatmind-registers.xlsx
@@ -11,6 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch markets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review findings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entitlements" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4018,4 +4022,8718 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>review_ref</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>review_severity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>status_after_v2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_or_next_step</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>linked_items</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Free-plan download rule conflicts across documents</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Founder decision DEC-008: MP3 for personal use plus 5 commercial songs a month</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-20; REQ-F-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BUG-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Hum input entitlement on Free</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Melody input moved to Phase 2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BUG-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MIDI entitlement by plan</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>MIDI export moved to Phase 2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BUG-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Stem count by plan</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4 separated stems on paid plans</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23; entitlement-matrix.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Stem taxonomy conflicts</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Stem set fixed by the separation model: vocals; drums; bass; other</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23; TDD 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BUG-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Native versus separated stems claim</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Stems are separated after generation and described that way; deck rewrite must not claim native stems</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-07; Batch 4 deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Deck shows lock accuracy that was never measured</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Measure BPM and key adherence of the model; publish targets only after measurement</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BUG-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Content ID safelist tier conflict</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Safelist dropped; replaced by certificate and dispute pack</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BUG-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Content ID safelist marketed as shipped</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No claim-clearance promise anywhere (REQ-F-26)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-11; REQ-F-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BUG-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Ownership wording versus deliverable rights</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Partly resolved</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009 sets user ownership of whatever rights BeatMind holds; certificate wording needs counsel sign-off</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-22; REQ-F-26; Batch 4 legal pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BUG-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Song length by plan</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30 s to 4 min for all plans in MVP</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BUG-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Studio plan timing</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Studio is Phase 2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>PRD 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BUG-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Prices missing in deck</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Price bands in Batch 4 financial model</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>PRD 9; Batch 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Launch wedge conflict</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Creators first; then artists; then producers</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>DEC-102</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BUG-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>API timing conflict</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Public API is Phase 3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>BUG-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Two latency definitions</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Single SLO: song playable within 60 s at p95 in beta</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Voice verification called identity check</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Voice models removed from MVP</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Training data under licence only claim</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Claim must not appear; disclose open-model data risk</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>RISK-001; A-024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Rendered audio not verified against locks</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Post-generation check of tempo and key; retry or label mismatch</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>No rule for conflicting inputs</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Input validation rules in API-001</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>F1.3</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Limited meters; no tempo or key changes</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Out of MVP scope</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>F1.4</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>No Unicode normalisation or injection rules for prompts and lyrics</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>NFC normalisation; strip zero-width and confusables before checks; prompt-injection guard for the lyric model</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>F1.5</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Lyric model may reproduce copyrighted lyrics</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Lyric similarity check against known lyrics where a lawful index exists; refuse known titles; log</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-52; TD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>F2.1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>No failure states for poor hum recordings</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Hum input is Phase 2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>F2.2</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Transcription flattens Indian ornamentation</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Hum input is Phase 2</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>F2.3</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Uploaded media parsed without sandboxing</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>No uploads in MVP; sandbox required when added</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-21; FEAT-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>F2.4</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Hummed copyrighted melody logged as human input</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Hum input is Phase 2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>F3.1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>No refund rules for failed or withheld takes</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Automatic credit refund for failed; timed-out or withheld takes</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-56</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>F3.2</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Final render may not sound like chosen draft</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>MVP generates full takes with one model; no separate render</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-05; TDD 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>F3.3</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Account farming of free generation</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Turnstile; device and payment fingerprints; daily caps; phone verification for free commercial licences</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>RISK-008; REQ-SEC-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>F3.4</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>No concurrency limit per user</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Per-user concurrent job limit by plan</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-55</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>F4.1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>No measurable seam quality test</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Seam test with onset and spectral discontinuity thresholds</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>F4.2</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Edits re-screen the whole take</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Screen only changed regions plus a context window</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>TDD 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>F4.3</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Unbounded take storage</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Per-plan storage quota and take limit per song</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>entitlement-matrix.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>F4.4</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Lyric-line edit syllable changes</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Lyric-line edit not in MVP</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>F5.1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Native stems unproven</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Separated stems only</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>F5.2</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Stem groups cannot produce eight named stems</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Four stems</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>BUG-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>F5.3</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>MIDI may not match audio</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>MIDI in Phase 2</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>BUG-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>F5.4</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Stem bleed not measured</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Disclose that separated stems can contain bleed; measure SDR on test set</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-23-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>BUG-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>F5.5</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Layered watermarks on stems</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Watermark only the mix and the export bundle manifest; record stems in ledger</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>ADR-010; TD-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>BUG-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>F6.1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Certificate of ownership overstates rights</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Partly resolved</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Certificate states transfer of BeatMind's rights; never claims copyright exists</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-22; REQ-F-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>BUG-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>F6.2</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Licensor terms may restrict output use</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Resolved for now</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>No licensors in Phase 1; model licences checked (C-02)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>ADR-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>BUG-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>F6.3</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Subscribe; bulk download; charge back</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Paid ownership vests only for songs created while payment settled; chargeback revokes ownership of songs created in the disputed period</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-57</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>BUG-044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>F6.4</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Free-song upgrade has no price or rules</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Rule and price in Batch 4</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>BUG-045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>F6.5</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Access after cancellation undefined</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Owned songs stay downloadable after cancellation (free-tier quotas apply to new creation)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-58</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>BUG-046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>F7.1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Authorship report certifies false human input</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Report says inputs are user-declared; no originality certification; terms make users warrant their inputs</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-31; Batch 4 legal pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>BUG-047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>F7.2</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Single signing key; 24-hour anchoring window</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Key in managed KMS; rotation; hourly digest</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-07; ADR-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>BUG-048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>F7.3</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Watermark not robust to adversarial removal</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Layered provenance; robustness test suite; never treat watermark absence as proof</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>TD-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>BUG-049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>F7.4</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Watermark presence proves only partial use</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Verify page reports match coverage and take; certificate tied to the full file hash</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>BUG-050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>F7.5</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Provenance retention versus erasure</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>DPIA decision: keep pseudonymous ledger with legal-claims basis; counsel to confirm</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>dpia.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>BUG-051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>F8.1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Distributor acceptance of disclosure</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Release pipeline is Phase 2</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>BUG-052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>F8.2</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Verify page is a free oracle</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Rate limits; Turnstile; file size cap; coarse answers to anonymous users</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>BUG-053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>F8.3</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Verify page leaks unreleased song metadata</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Show details only for public songs or to the certificate holder</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>BUG-054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>F9.1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>No Content ID clearance lever</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>No clearance promised; dispute pack only</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>BUG-055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>F9.2</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Channel OAuth scopes undefined</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>No channel linking in MVP</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>BUG-056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>F9.3</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Licence scope for networks and reuploads undefined</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Define in licence terms</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Batch 4 legal pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>BUG-057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>F10.1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Voice verification can be spoofed</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Voice models removed from MVP</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>BUG-058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>F10.2</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Protected-voice registry undefined</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>With FEAT-30</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>BUG-059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>F10.3</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Biometric consent mechanics</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>With FEAT-30</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>BUG-060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>F10.4</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Deleted voice model breaks songs</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>With FEAT-30</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>BUG-061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>F10.5</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Account takeover exposes voice</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>With FEAT-30</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>BUG-062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>F11.1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Upload fingerprinting evadable</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>No uploads in MVP</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>BUG-063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>F11.2</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Similarity thresholds untuned</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Build labelled test set; set false-positive and false-negative targets before beta</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>TD-03; TC-REQ-F-52-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>BUG-064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>F11.3</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Similarity index coverage too narrow</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Choose reference index source</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>TD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>BUG-065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>F11.4</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Moderation not multilingual</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Multilingual moderation incl. Devanagari and romanised Hindi; transliteration-aware artist list</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-51; REQ-SEC-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>BUG-066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>F11.5</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>No appeal path</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Appeal button and human review queue in admin</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-59</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>BUG-067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>F12.1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Insecure direct object references</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Owner-based authorisation on every resource; random non-sequential IDs; tests</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>BUG-068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>F12.2</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Private links never expire</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Revocable share tokens; signed URLs expire in 15 minutes</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>BUG-069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>F12.3</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Public page abuse</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Moderate titles and lyrics before publishing; link stripping; report button</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-50; REQ-F-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>BUG-070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>F12.4</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Search assumes Latin text</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Unicode-aware search with transliteration</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>BUG-071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>F13.1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>No entitlement matrix</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Entitlement matrix created</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>entitlement-matrix.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>BUG-072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>F13.2</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>No user MFA</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Optional TOTP or passkey; required for admins</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>BUG-073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>F13.3</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Age gate without verification; DPDP parental consent</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>18+ only in India for beta; parental-consent flow before allowing under-18s</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-53</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>BUG-074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>F13.4</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Card-only payments</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Razorpay with UPI in India</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>ADR-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>BUG-075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>F13.5</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>No fraud controls on credits</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Provider fraud tools; velocity limits</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>BUG-076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>F14.1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>GPU time per job assumed</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Benchmark in Sprint 1; cost alert</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>A-025; REQ-NFR-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>BUG-077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>F14.2</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>GPU supply for scale-up assumed</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Multi-provider worker images; API fallback with cap</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>ADR-006; ADR-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>BUG-078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>F14.3</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Fingerprint vendor rate limits</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Self-hosted fingerprinting; async screening queue</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>INT-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>BUG-079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>F14.4</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Merkle root growth</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Per-song chains plus daily signed digest of changed songs only</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>ADR-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>BUG-080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>F14.5</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>No South Asia region</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>India-first hosting region</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>TDD 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>BUG-081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>F14.6</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>No load shedding for verify and public pages</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Separate rate limits and CDN caching; shed verify before generation</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>BUG-082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Indic text length and normalisation</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Count grapheme clusters; store UTF-8 NFC; bidi support; embed fonts in PDFs</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>BUG-083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Moderation not multilingual</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Launch-blocking</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Same as F11.4; native-speaker review queue</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>BUG-084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Singing pronunciation per language</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Language gate G1 per language</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>PRD 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>BUG-085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Western music theory assumptions</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Indic music engine in Phase 3 (U7)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>BUG-086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>No regional training data</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Model choice and G1; licensed regional data after funding</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>RISK-003; FEAT-33</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>BUG-087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Cultural and legal content rules by market</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Per-market content policy reviewed by local counsel</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>compliance-register.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>BUG-088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>US-centric payments</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>ADR-009 and PPP pricing</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>ADR-009; DEC-013</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>BUG-089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Lyric model quality per language</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Per-language lyric test</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>TD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>BUG-090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Metadata needs scripts and transliteration</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Store title in original script plus transliteration and language code</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-08</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>obligation_summary</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>applies_to_beatmind_when</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>beta_status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>implementing_controls</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>counsel_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Information Technology Act 2000 s.79 and IT (Intermediary Guidelines and Digital Media Ethics Code) Rules 2021</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Safe-harbour due diligence: publish terms, privacy policy and user rules; appoint a grievance officer; acknowledge and resolve user complaints within set timelines; act on lawful orders</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>BeatMind hosts user content (public song pages) for Indian users</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Likely applies</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge; verify with counsel</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-54; REQ-F-59; Batch 4 legal pack</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>IT Rules amendments on synthetically generated information (notified 2026-02-10; in force 2026-02-20)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Prominently label synthetic audio; embed permanent metadata or provenance markers with unique identifiers; do not allow markers to be removed; deploy technical measures against prohibited synthetic content; act on government or court orders within 3 hours</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>BeatMind offers tools that generate synthetic audio for Indian users</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Externally sourced</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SRC-117</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-30; REQ-F-33; REQ-F-54; ADR-010</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Required: confirm label format for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>IT Rules: significant social media intermediary duties</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Additional duties incl. user declaration and verification of synthetic content</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Only above 5 million registered users in India</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Externally sourced</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>SRC-117</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Monitor user count</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Before threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Act 2023 and DPDP Rules 2025 (notified November 2025; phased over 12 to 18 months)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Notice and consent; verifiable parental consent for children (under 18); reasonable security safeguards; breach intimation to the Board and affected users; erasure and retention limits; grievance redress; penalties up to ₹250 crore per breach</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Processing personal data of users in India</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Applies (phase dates to confirm, C-07)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Externally sourced (rules, penalty); Assumption (child age definition)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>SRC-118</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-53; REQ-NFR-05; dpia.md; consent table (TDD 5.1)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Act 1957; DPIIT working paper on generative AI and copyright (December 2025, under consultation)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Avoid infringing outputs; authorship of computer-generated works rests with the person who causes the work to be created (s.2(d)(vi)) [to confirm]; AI training exceptions unsettled</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>All generated outputs and model use</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Externally sourced (working paper); Assumption (s.2(d)(vi) reading)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>SRC-102</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-22; REQ-F-26; REQ-F-52; RISK-001; RISK-011</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Protection Act 2019; Consumer Protection (E-Commerce) Rules 2020; Guidelines on dark patterns (2023)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Clear seller details and prices incl. taxes; grievance officer; no subscription traps or drip pricing; easy cancellation</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Selling subscriptions to Indian consumers</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Applies at paid launch</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge; verify with counsel</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-40; REQ-F-43; UX spec section 6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Goods and Services Tax</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Register; charge GST on subscriptions (Suno's Indian prices include 18% GST, SRC-111); file returns</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Indian entity selling to Indian users</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Applies at paid launch</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Assumption (rate cross-checked against SRC-111)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>SRC-111</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Financial model (Batch 4)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Required (tax adviser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>RBI framework for e-mandates on recurring card and UPI payments</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Additional factor of authentication at mandate set-up; pre-debit notification; limits above which each charge needs authentication</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Recurring subscription charges in India</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Applies at paid launch</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge; handled largely by the payment provider</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>ADR-009; INT-09</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Confirm with Razorpay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Personality and publicity rights (case law)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Do not imitate the voice, name or likeness of identifiable persons without consent; Indian courts have granted injunctions to performers against AI voice imitation [to confirm cases]</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Prompts naming artists; voice features</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge; verify with counsel</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-50; FEAT-30 deferred</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>COMP-IN-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2013; foreign investment rules (FEMA) for fundraising</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Incorporation, statutory filings; compliant issue of shares to foreign investors</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>If founders incorporate in India (A-001)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Pending Q-F01</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>A-001</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Batch 4 diligence pack</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Required (company secretary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>COMP-EU-01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>AI Act Article 50 (applies from 2026-08-02; watermark sub-obligation runway to 2026-12-02)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Providers of systems generating synthetic audio must mark outputs in a machine-readable, detectable format; deployers must disclose deepfakes; fines up to €15M or 3% of turnover</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Placing the generator on the EU market or serving EU users</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Applies before serving EU users</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Externally sourced</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>SRC-119</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>ADR-010; C-06</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Required before Wave 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>COMP-EU-02</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>General Data Protection Regulation</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Lawful basis, transparency, data subject rights, DPIA where high risk, EU representative if no EU establishment, transfer safeguards</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Offering services to people in the EU</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Applies before serving EU users</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge; verify with counsel</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>dpia.md; REQ-NFR-05</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Required before Wave 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>COMP-EU-03</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Digital Services Act</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Notice-and-action for illegal content, statements of reasons, points of contact; lighter duties for micro and small enterprises</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Hosting user content for EU users</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Applies before serving EU users</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge; verify with counsel</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-54; REQ-F-59</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Required before Wave 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>COMP-EU-04</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Consumer law on digital content and VAT</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Withdrawal-right rules for digital content; VAT on digital services (merchant of record handles VAT collection)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Selling to EU consumers</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Applies before paid EU sales</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>ADR-009</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Required before Wave 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>COMP-US-01</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Office guidance (Part 2 report, 2025-01-29)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Purely AI-generated material is not protected; human expressive contributions, selection and arrangement may be</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>US users registering works</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Applies (information duty to users)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Externally sourced</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>SRC-120</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-26; authorship report wording</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>COMP-US-02</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DMCA s.512 safe harbour</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Designate an agent with the Copyright Office; notice-and-takedown; repeat-infringer policy</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Hosting user content accessible in the US</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Likely applies</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-54</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>COMP-US-03</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>State right-of-publicity and voice laws</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Do not commercially imitate a person's voice or likeness without consent</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Voice and artist imitation</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-50</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>COMP-US-04</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Children's Online Privacy Protection Act</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Parental consent before collecting data from under-13s</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Only if under-13s use the service</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable in beta (18+ only)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-53</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-53</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>COMP-GL-01</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Model licences (ACE-Step MIT or Apache-2.0; Stability Community Licence; Lyria API terms)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Keep licence and notice files; respect revenue thresholds and use restrictions</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Using third-party models</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Source-stated</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>SRC-105; SRC-106; SRC-108</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>model-register.md; C-02</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>COMP-GL-02</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Open-source licences of dependencies</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Meet attribution and copyleft obligations (for example LGPL linking terms)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Shipping software with open-source components</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>CI licence scan (testing strategy section 6)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>COMP-GL-03</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Payment Card Industry Data Security Standard</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Keep card data out of BeatMind systems; hosted checkout keeps scope minimal</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Taking card payments</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Applies at paid launch</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Analyst knowledge</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>ADR-009</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>COMP-GL-04</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Sanctions regimes</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Block sanctioned regions and persons from paid services</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Selling internationally</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Applies at paid launch</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>RISK-012; A-023</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Geo-blocking at checkout</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>COMP-GL-05</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Distributor and platform AI policies (YouTube; DistroKid; Spotify)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Disclose AI use; follow upload rules</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Users releasing songs</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-22</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>COMP-SA-01</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Pakistan; Bangladesh; Nepal</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Local cybercrime, content and data laws</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Unknown until local counsel review</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2 launch</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Wave 2 gate</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Required before Wave 2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>requirement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>test_case</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-01-01</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Description prompt returns two playable takes</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-01-02</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>p95 time to playable under 60 s at beta load</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>k6</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-02</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-02</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-02-01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Accepts 3,000 grapheme clusters of Devanagari; rejects 3,001</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-02</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-02</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-02-02</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Hinglish and English lyrics accepted; vocal type and instrumental toggle honoured</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5 + Testcontainers</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-03</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-03-01</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Lyric writer returns verse, chorus and bridge sections in requested language</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-03</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-03-02</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Native-speaker review of 50 lyric samples per language</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Review sheet</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-04</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-04</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-04-01</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Beat request validates BPM 60-200, key and instrument lists</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-04</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-04</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-04-02</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Detected tempo within ±3 BPM and key matches in target share of takes</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Model eval</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>pytest + librosa</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-05</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-05</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-05-01</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Two takes per request; keep, regenerate and discard work</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-06</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-02</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-06-01</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Lengths 30 s and 4 min produced within ±5 s</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Model eval</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-07</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-16</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-07-01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Language not passed G1 is hidden or marked experimental</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-08</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-16</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-08-01</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Text stored NFC; grapheme counting; transliteration and language tag stored</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-08</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-16</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-08-02</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Certificate PDF renders Devanagari correctly</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5 + PDF text extraction</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-10</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-06</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-10-01</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Extend, trim, fade and section regenerate create new versions</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-10</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-06</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-10-02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Seam test: no onset or spectral discontinuity above threshold at edit boundaries</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Model eval</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-11</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-06</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-11-01</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Compare and restore earlier version</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-20</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-07</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-20-01</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Free MP3 192 kbps download carries attribution metadata</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-21</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-21-01</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Sixth commercial licence in a calendar month is refused</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-21</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-21-02</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Counter resets at month boundary in user's billing time zone</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-22</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-22-01</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Paid-plan song created with user_owned state and certificate wording approved by counsel</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-07</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-23-01</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Paid user downloads WAV 48 kHz 24-bit and MP3 320</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-07</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-23-02</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Four stems produced and sum to mix within tolerance</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Model eval</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-07</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-23-03</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Stem separation quality (SDR) reported on test set</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Model eval</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-24-01</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Free song conversion rule applied (after Batch 4 rule)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-25-01</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Cancelling does not change rights_status of existing songs</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-26-01</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Copy check: no string promises copyright protection or claim-free use</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Copy lint script</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-30</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-10</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-30-01</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Exported files carry AI label metadata, valid C2PA manifest and detectable watermark</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>pytest + c2patool</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-31</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-10</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-31-01</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Every generation, edit and export appends a ledger event; chain verifies</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-31</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-10</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-31-02</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Tampered event breaks chain verification</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-32</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-10</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-32-01</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Verify page identifies BeatMind file and reports coarse answer to anonymous users</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-33</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-10</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-33-01</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>AI-generated label visible on song page, embed and download dialog</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-40</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-08</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-40-01</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Price shown in local currency for each band country</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-41</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-08</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-41-01</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Billing country of payment method overrides browsing country</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-42</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-08</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-42-01</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>UPI, card and net banking checkout in Razorpay test mode</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5 + provider sandbox</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-43</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-08</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-43-01</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Cancellation completes in three steps or fewer</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-50</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-14</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-50-01</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Artist names in Latin, Devanagari and romanised Hindi blocked</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-50</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-14</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-50-02</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Unicode attack corpus does not bypass block</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-51</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-14</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-51-01</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Lyric moderation red-team set in three languages: no prohibited output passes</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Model eval</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-52</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-14</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-52-01</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Similarity screen withholds known near-copies in labelled set at target rates</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Model eval</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-53</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-15</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-53-01</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Under-18 date of birth blocks sign-up</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-54</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-18</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-54-01</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Takedown disables song and notifies user; 3-hour order path works end to end</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-55</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-17</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-55-01</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Daily cap and concurrency limit enforced per plan</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-56</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-08</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-56-01</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Failed, timed-out and withheld takes refund credits with ledger entry</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-57</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-57-01</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Chargeback webhook reverts rights of songs from the disputed period</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-58</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-58-01</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled user can still download owned songs</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-59</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-18</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-F-59-01</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Appeal creates review case visible in admin queue</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-01</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-01-01</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Latency SLO measured under load profile</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>k6</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-02</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-02-01</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Availability measured over 4 beta weeks</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Grafana SLO</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-03</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-03-01</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Horizontal scale test: doubling API replicas roughly doubles throughput</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>k6</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-04</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-04-01</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>OWASP ASVS level 2 checklist completed</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>ASVS sheet</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-05</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-05-01</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Data export and deletion work end to end</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-06</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-06-01</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>No clipping; loudness of previews within ±1 LU of target</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Model eval</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>pytest + pyloudnorm</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-07</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-07-01</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Cost per song metric emitted and alert fires above ceiling</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>JUnit 5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-08</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-08-01</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>axe-core: zero serious or critical violations on all pages</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Automated a11y</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Playwright + axe-core</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-08</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-08-02</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Manual screen-reader pass (NVDA, TalkBack) on core flows</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-09</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-09-01</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>All UI strings externalised; Hindi locale renders without overflow</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-10</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-NFR-10-01</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Core flows on a 3 GB RAM Android phone over throttled 4G</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Device lab or emulator</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-01</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-01-01</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-02</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-02-01</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-03</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-03-01</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-04</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-04-01</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-05</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-05-01</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-06</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-06-01</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-07</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-07-01</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-08</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-08-01</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-09</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-09-01</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-10</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-10-01</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-11</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-11-01</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-12</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-12-01</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-13</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-13-01</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-14</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-14-01</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-15</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>TC-REQ-SEC-15-01</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>See threat model section 5 verification column</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>See threat-model.md</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>entitlement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>creator</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>studio_phase2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Song and beat generation</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Daily cap set by admin</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Monthly credits</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Higher monthly credits</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Team credits</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-01; REQ-F-55</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Takes per request</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Concurrent generation jobs</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-55</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Song length</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>30 s to 4 min</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>30 s to 4 min</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30 s to 4 min</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30 s to 4 min</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Launch languages that passed G1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AI lyric writer</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Editor (extend; trim; fade; section regenerate)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Trim and fade only</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MP3 download</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>192 kbps personal use</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>320 kbps</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>320 kbps</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>320 kbps</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-20; REQ-F-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>WAV download</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Separated stems (vocals; drums; bass; other)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Commercial use</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>5 songs per month with attribution (A-005)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>All songs</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>All songs</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>All songs</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Ownership of songs created on plan</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>BeatMind owns; user licensed</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>User owns</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>User owns</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Organisation owns</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Licence certificate</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>For the 5 licensed songs</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Every song</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Every song</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Every song</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Dispute pack for claims</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Priority queue</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>PRD 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Storage quota (kept takes)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>100 takes</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2000 takes</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10000 takes</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Team pool</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Public song page and embed</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Optional MFA</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Required for admins</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Team workspace and invoices</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-24</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/registers/beatmind-registers.xlsx
+++ b/docs/registers/beatmind-registers.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entitlements" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12736,4 +12737,1786 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>epic_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>acceptance_criteria</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>linked</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>target_sprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>US-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EP-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Foundations: repo, CI, environments, observability</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>As a developer, I want a monorepo with Java, Python and web modules building in CI, so that every change is tested</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>CI runs unit tests, scans and RTM check on every pull request; main is protected</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SEC-12</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>US-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>EP-01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Foundations: repo, CI, environments, observability</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>As a developer, I want Docker Compose for local development with a CPU model stub, so that I can work without a GPU</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>`docker compose up` starts web, API, Postgres, Valkey, MinIO and stub worker; README documents it</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>US-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>EP-01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Foundations: repo, CI, environments, observability</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>As an operator, I want staging and production environments defined in OpenTofu, so that environments are reproducible</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Plan and apply succeed from CI; secrets from vault</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>ADR-006; ADR-012</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>US-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EP-01</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Foundations: repo, CI, environments, observability</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>As an operator, I want OpenTelemetry traces, metrics and logs with dashboards, so that I can see SLOs</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Dashboards for latency, errors, queue depth, GPU use, cost per song</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-07</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>US-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>EP-03</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Generation pipeline</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>As the team, I want ACE-Step 1.5 benchmarked on a rented GPU, so that we know real time and cost per take</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Report with seconds per take, VRAM, cost per take for 3 GPU types; licence file archived</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>A-025; C-02</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>US-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>EP-04</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Lyrics and languages</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>As the team, I want a Hindi and Hinglish quality spike, so that we know if the beachhead language works</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20 prompts per language generated and scored by 3 native speakers; go or fallback decision</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>A-021; RISK-003</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>US-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>EP-12</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Validation and growth (waitlist, interviews, listening tests)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>As the founder, I want a waitlist page with local prices shown, so that we measure interest and price response</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Page live in English and Hindi; sign-ups stored with consent; price variant recorded</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>H-001; H-004</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>US-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>EP-12</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Validation and growth (waitlist, interviews, listening tests)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>As the founder, I want 20 creator interviews done with a script, so that demand hypotheses are tested</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Interview notes in repository; synthesis against H-001 to H-005</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>DEC-012</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>US-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>EP-02</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Identity and accounts</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>As a creator, I want to sign in with Google or an email code, so that I can start quickly</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in works; sessions secure per REQ-SEC-01; 18+ check at sign-up</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-53; REQ-SEC-01</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>US-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>EP-02</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Identity and accounts</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to choose English or Hindi, so that the app speaks my language</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Locale switch persists; all MVP strings in both languages</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-16; REQ-NFR-09</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>US-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>EP-02</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Identity and accounts</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to export or delete my data, so that I control my information</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Export JSON plus files; deletion per DPIA section 6</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-05</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>US-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>EP-03</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Generation pipeline</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>As a creator, I want to describe a vibe and get two takes, so that I get music for my video</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>API-001 and API-002 with SSE; two takes delivered; p95 under 60 s in staging</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-01; REQ-F-05</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>US-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>EP-03</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Generation pipeline</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>As the system, I want a durable Postgres job queue with retries and dead-letter, so that jobs survive restarts</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Jobs claimed with SKIP LOCKED; retry with backoff; dead-letter visible in admin</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ADR-005</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>US-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>EP-03</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Generation pipeline</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>As a creator, I want to see my queue position and wait time, so that I know when my song is ready</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Live region announces status; estimate within ±30%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>UX-A11Y-15</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>US-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>EP-03</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Generation pipeline</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>As a producer, I want Beat mode with genre, BPM, key and instruments, so that I can make instrumentals</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Validation per REQ-F-04; tempo check runs on output</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-04</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>US-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>EP-03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Generation pipeline</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>As the system, I want a Lyria fallback with a daily spend cap, so that paid users still get songs when GPUs are busy</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Fallback used only when routed; cap enforced; cost logged</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ADR-007; REQ-SEC-09</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>US-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>EP-04</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Lyrics and languages</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>As an artist, I want to paste lyrics in Hindi, Hinglish or English, so that my words become a song</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Grapheme counting; NFC; language tag stored; custom mode works</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-02; REQ-F-08</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>US-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>EP-04</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Lyrics and languages</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>As a creator, I want the AI to write lyrics from a topic and mood, so that I can make a song without writing</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Sectioned lyrics in chosen language; moderation applied</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-03</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>US-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>EP-05</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Provenance, labelling and certificates</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>As the system, I want every event written to a hash-chained ledger, so that provenance is provable</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Chain verification test passes; tamper test fails as expected</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-31; REQ-SEC-07</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>US-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>EP-05</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Provenance, labelling and certificates</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want my downloads labelled and watermarked with content credentials, so that they meet AI rules</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>AI label metadata, valid C2PA manifest, detectable watermark on every export</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-30; COMP-IN-02</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>US-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>EP-05</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Provenance, labelling and certificates</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>As anyone, I want to verify a file or certificate, so that I can check its origin</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Verify page with rate limits and coarse anonymous answers</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-32; REQ-SEC-10</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>US-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Library, player and sharing</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>As a creator, I want a library of my songs and takes, so that I can find my work</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>List, search (Unicode-aware), rename, delete</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-12</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>US-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Library, player and sharing</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>As a creator, I want an accessible player that shows lyrics and the AI label, so that everyone can use it</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Keyboard operable; ARIA; lyrics shown; label visible</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-33; UX-A11Y-01 to 03</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>US-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>EP-06</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Library, player and sharing</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>As a creator, I want to share a private link or public page, so that others can hear my song</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Revocable share tokens; public page with moderation of title and lyrics</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-13; REQ-SEC-03</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>US-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>EP-07</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Rights, quotas and downloads</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>As a free user, I want to mark up to 5 songs a month for commercial use, so that I can use them in videos</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Quota enforced; certificate issued; attribution text provided</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-21</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>US-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>EP-07</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Rights, quotas and downloads</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to download MP3 (and WAV when paid), so that I can use my song</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Signed URLs 15 min; formats by plan per entitlement matrix</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-20; REQ-F-23</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>US-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>EP-07</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Rights, quotas and downloads</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want failed or withheld takes refunded, so that I never pay for nothing</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Automatic refund with ledger entry</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-56</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>US-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>EP-08</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Safety and moderation</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>As the platform, I want prompts and lyrics moderated in Hindi, Hinglish and English, so that harmful content is blocked</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Red-team set passes; Unicode corpus passes; reasons shown</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-50; REQ-F-51; REQ-SEC-04</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>US-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>EP-08</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Safety and moderation</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>As the platform, I want generated audio screened for similarity, so that near-copies are withheld</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Screen runs on every take; withheld takes logged and refunded</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-52</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>US-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>EP-08</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Safety and moderation</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>As the platform, I want bot defence and caps, so that free generation is not abused</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Turnstile; daily caps; concurrency limits; velocity rules</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-55; REQ-SEC-09</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>US-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>EP-09</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Admin and takedowns</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>As an admin, I want a console for users, caps and the moderation queue, so that I can run the beta</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Role-gated; MFA required; every action audited</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-18; REQ-SEC-06</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>US-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>EP-09</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Admin and takedowns</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>As an admin, I want takedown and appeal workflows with deadline timers, so that we meet the 3-hour rule</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Orders path tested end to end; appeals queue works</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-54; REQ-F-59</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>US-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>EP-10</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Payments and pricing</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to see prices in my currency for my country, so that the price is fair where I live</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Price bands applied by billing country</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-40; REQ-F-41</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>US-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>EP-10</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Payments and pricing</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>As an Indian user, I want to pay by UPI, card or net banking, so that I can subscribe</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Razorpay test and live mode; webhooks verified</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-42; REQ-SEC-08</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>US-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>EP-10</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Payments and pricing</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>As an international user, I want to pay through a merchant of record, so that taxes are handled</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Provider checkout; webhooks verified</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>ADR-009</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>US-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>EP-10</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Payments and pricing</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>As a paid user, I want ownership of songs I create, with a certificate, so that I can use them anywhere</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>user_owned state; certificate; vesting on settlement; chargeback rule</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-22; REQ-F-57</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>US-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>EP-10</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Payments and pricing</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to cancel online easily and keep my owned songs, so that I trust the service</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Three-step cancel; downloads still available</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-43; REQ-F-58</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>US-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>EP-11</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Editor and stems</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>As a creator, I want to extend, trim, fade and regenerate a section, so that I can fix a take</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>New version per edit; seam test passes</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-10; REQ-F-11</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>US-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>EP-11</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Editor and stems</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>As a producer, I want four separated stems, so that I can mix my song</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Demucs stems; sum test; SDR reported</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>REQ-F-23</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>US-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>EP-12</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Validation and growth (waitlist, interviews, listening tests)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>As the team, I want G1 listening tests run for Hindi, Hinglish and English, so that we know which languages launch</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>30 listeners per language; results against pass mark</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>PRD 12</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>US-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>EP-12</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Validation and growth (waitlist, interviews, listening tests)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>As the founder, I want an investor demo script and recording, so that fundraising can start</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Five-minute demo of the beta flow on staging</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>A-003</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>US-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>EP-01</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Foundations: repo, CI, environments, observability</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>As the team, I want a load test and a security baseline scan before beta, so that gate G2 is met</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>k6 at 2x beta peak; ZAP baseline; findings triaged</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-01; REQ-SEC-12</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>US-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>EP-01</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Foundations: repo, CI, environments, observability</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>As the team, I want accessibility checks in CI and a manual screen-reader pass, so that WCAG 2.2 AA holds</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>axe-core in CI; manual pass recorded</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NFR-08</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>SPRINT-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/registers/beatmind-registers.xlsx
+++ b/docs/registers/beatmind-registers.xlsx
@@ -448,7 +448,7 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="43" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,17 +506,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Founders are based in India and will register an Indian private limited company</t>
+          <t>Founders and developers are in India; an Indian private limited company will be registered</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Source-stated</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Default for Q-F01</t>
+          <t>Founder answer</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Confirmed by founder 2026-10-29 (DEC-022)</t>
         </is>
       </c>
     </row>
@@ -553,17 +553,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Founders can spend nothing monthly before funding (₹0)</t>
+          <t>Founders can spend ₹5,000 to ₹10,000 a month before funding</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Source-stated</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Default for Q-F02</t>
+          <t>Founder answer</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Confirmed by founder 2026-10-29 (DEC-023)</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>January 2027 means investor demo and invite-only beta; public launch later</t>
+          <t>January 2027 means a closed beta; final plan set by testing and bug fixes</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Source-stated</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Default for Q-F03</t>
+          <t>Founder answer</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Confirmed by founder 2026-10-29 (DEC-024)</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Source-stated</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Default for Q-F05; DEC-008</t>
+          <t>Founder answer</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Confirmed by founder 2026-10-29 (DEC-025)</t>
         </is>
       </c>
     </row>
@@ -741,17 +741,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Each developer works about 40 hours a week</t>
+          <t>Each developer works 30 to 50 hours a week; plans use 30</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Source-stated</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Default for Q-F06</t>
+          <t>Founder answer</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Confirmed by founder 2026-10-29 (DEC-026)</t>
         </is>
       </c>
     </row>

--- a/docs/registers/beatmind-registers.xlsx
+++ b/docs/registers/beatmind-registers.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Source-stated</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Default for Q-F04</t>
+          <t>Founder answer</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Confirmed by founder 2026-10-29 (DEC-027)</t>
         </is>
       </c>
     </row>
